--- a/db/sctype.beta.xlsx
+++ b/db/sctype.beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hua/Documents/_Toolkit/_singleCell/2.celltypeAnno/public_version/cte.v0.3.2/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3352005A-9997-784A-84DA-B0D3363F44D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B834507-7C7A-4440-BBEC-F224E641F127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="11220" windowWidth="25980" windowHeight="9840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2860" yWindow="6120" windowWidth="28600" windowHeight="15340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="424">
   <si>
     <t>tissueType</t>
   </si>
@@ -451,9 +451,6 @@
     <t>ISG+</t>
   </si>
   <si>
-    <t>Microglial</t>
-  </si>
-  <si>
     <t>Myelinating Schwann</t>
   </si>
   <si>
@@ -469,9 +466,6 @@
     <t>Non myelinating Schwann</t>
   </si>
   <si>
-    <t>Radial glial</t>
-  </si>
-  <si>
     <t>Schwann precursor</t>
   </si>
   <si>
@@ -715,21 +709,12 @@
     <t>ScType</t>
   </si>
   <si>
-    <t>Cycling progenitors</t>
-  </si>
-  <si>
-    <t>CycProg</t>
-  </si>
-  <si>
     <t>Cell cycling</t>
   </si>
   <si>
     <t>Cortex</t>
   </si>
   <si>
-    <t>PMID: 30089906</t>
-  </si>
-  <si>
     <t>Ependymal cells</t>
   </si>
   <si>
@@ -739,17 +724,587 @@
     <t>PMID: 34321664; PMID: 34912118</t>
   </si>
   <si>
-    <t>TOP2A,MKI67,CDK1</t>
-  </si>
-  <si>
     <t>FOXJ1,TMEM212,Sparcl1,Dynlrb2,Deup1,Ccdc153,Foxn4,Meig1,Tekt4,Gja1,Cybrd1,Lrrc23,Dmkn,Cdc20b,Pifo,Rarres2,Rsph1</t>
+  </si>
+  <si>
+    <t>Hypothalamus</t>
+  </si>
+  <si>
+    <t>Glutamatergic (Glut)</t>
+  </si>
+  <si>
+    <t>Slc17a7,Slc17a8,Slc17a6</t>
+  </si>
+  <si>
+    <t>Neuron</t>
+  </si>
+  <si>
+    <t>Glut</t>
+  </si>
+  <si>
+    <t>Neruon</t>
+  </si>
+  <si>
+    <t>Whole brain</t>
+  </si>
+  <si>
+    <t>PMID: 37034735</t>
+  </si>
+  <si>
+    <t>GABAergic (GABA)</t>
+  </si>
+  <si>
+    <t>Slc32a1,Slc18a2,Gad2,Aldh1a1,Gad1</t>
+  </si>
+  <si>
+    <t>Glycinergic (Glyc)</t>
+  </si>
+  <si>
+    <t>Slc6a5</t>
+  </si>
+  <si>
+    <t>Glyc</t>
+  </si>
+  <si>
+    <t>Cholinergic (Chol)</t>
+  </si>
+  <si>
+    <t>Chat,Slc18a3</t>
+  </si>
+  <si>
+    <t>Chol</t>
+  </si>
+  <si>
+    <t>Dopaminergic (Dopa)</t>
+  </si>
+  <si>
+    <t>Slc18a2,Th,Slc6a3,Ddc</t>
+  </si>
+  <si>
+    <t>Dopa</t>
+  </si>
+  <si>
+    <t>Serotonergic (Sero)</t>
+  </si>
+  <si>
+    <t>Tph2,Slc18a2,Ddc,Slc6a4</t>
+  </si>
+  <si>
+    <t>Sero</t>
+  </si>
+  <si>
+    <t>Noradrenergic (Nora)</t>
+  </si>
+  <si>
+    <t>Slc6a2,Slc18a2,Dbh</t>
+  </si>
+  <si>
+    <t>Nora</t>
+  </si>
+  <si>
+    <t>Histaminergic (Hist)</t>
+  </si>
+  <si>
+    <t>Hdc,Slc18a2</t>
+  </si>
+  <si>
+    <t>Hist</t>
+  </si>
+  <si>
+    <t>Fibroblasts</t>
+  </si>
+  <si>
+    <t>Col3a1,Col6a3</t>
+  </si>
+  <si>
+    <t>Fibroblast</t>
+  </si>
+  <si>
+    <t>PMID: 32769974;PMID: 33560373</t>
+  </si>
+  <si>
+    <t>A2m,Ets1,Vwf,Tm4sf1,Gata2,Xdh,Pecam1,Vcam1,Flt1,Cldn5,Apold1,Cd34,Eng,Mcam,Lef1,Foxc1,Cdh5</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>PMID: 34163074;ScType; PMID: 32404418</t>
+  </si>
+  <si>
+    <t>Glutamatergic neurons (mixed)</t>
+  </si>
+  <si>
+    <t>Dync1i1,Satb2,Fezf2</t>
+  </si>
+  <si>
+    <t>glutamatergic neurons (Glut)</t>
+  </si>
+  <si>
+    <t>Manual;PMID: 34321664;PMID: 34163074</t>
+  </si>
+  <si>
+    <t>TOP2A,MKI67,CDK1,CLSPN,AURKA,MCM2,TYMS,HMGB2</t>
+  </si>
+  <si>
+    <t>PMID: 30089906;PMID: 34390642;PMID: 32663469</t>
+  </si>
+  <si>
+    <t>NEC</t>
+  </si>
+  <si>
+    <t>ScType DB</t>
+  </si>
+  <si>
+    <t>HES1,ATP1A2,VIM</t>
+  </si>
+  <si>
+    <t>RGC</t>
+  </si>
+  <si>
+    <t>Radial glia</t>
+  </si>
+  <si>
+    <t>PMID: 34390642;PMID: 37704762(VIM);</t>
+  </si>
+  <si>
+    <t>Ventricular radial glial cells</t>
+  </si>
+  <si>
+    <t>FBXO32,CTGF,CYR61</t>
+  </si>
+  <si>
+    <t>PMID: 34390642</t>
+  </si>
+  <si>
+    <t>Early radial glial cells</t>
+  </si>
+  <si>
+    <t>NPY,FGFR3</t>
+  </si>
+  <si>
+    <t>Late radial glial cells</t>
+  </si>
+  <si>
+    <t>CD9,GPX3,TNC</t>
+  </si>
+  <si>
+    <t>Outer radial glial cells</t>
+  </si>
+  <si>
+    <t>MOXD1,HOPX,FAM107A,MT3</t>
+  </si>
+  <si>
+    <t>Truncated radial glial cells</t>
+  </si>
+  <si>
+    <t>CRYAB,NR4A1,FOXJ1</t>
+  </si>
+  <si>
+    <t>Multipotent glial progenitor cells</t>
+  </si>
+  <si>
+    <t>ASCL1,OLIG2,PDGFRA,EGFR</t>
+  </si>
+  <si>
+    <t>mGPC</t>
+  </si>
+  <si>
+    <t>Oligodendrocyte precursor cells/Oligodendrocytes</t>
+  </si>
+  <si>
+    <t>SOX10,NKX2-2,MBP</t>
+  </si>
+  <si>
+    <t>OPC/Oligo</t>
+  </si>
+  <si>
+    <t>UGT8,MBP,PLP1,MOBP,OLG2,MOG</t>
+  </si>
+  <si>
+    <t>Oligo</t>
+  </si>
+  <si>
+    <t>Glia</t>
+  </si>
+  <si>
+    <t>PMID: 34616062;https://www.proteinatlas.org/humanproteome/brain/human+brain;PMID: 34390642 Table S1G;PMID: 26060302; PMID: 32663469</t>
+  </si>
+  <si>
+    <t>PDGFRA,LHFPL3,MEGF11,PCDH15,OLIG2,GPR17,OLIG1,APOD</t>
+  </si>
+  <si>
+    <t>PMID: 34616062;PMID: 34390642;PMID: 26060301; PMID: 32663469</t>
+  </si>
+  <si>
+    <t>AQP4,APOE,GFAP,GLI3,SLC1A3</t>
+  </si>
+  <si>
+    <t>Astrocyte</t>
+  </si>
+  <si>
+    <t>PMID: 34390642;PMID: 34616062;PMID: 26060301;https://www.proteinatlas.org/humanproteome/brain/human+brain</t>
+  </si>
+  <si>
+    <t>IPC</t>
+  </si>
+  <si>
+    <t>Neuronal intermediate progenitor cells</t>
+  </si>
+  <si>
+    <t>PPP1R17,PENK,NEUROG1,NEUROG2,EOMES,UNC5D</t>
+  </si>
+  <si>
+    <t>nIPC</t>
+  </si>
+  <si>
+    <t>PMID: 34390642;PMID: 30089906</t>
+  </si>
+  <si>
+    <t>DCX,NCAM1,NEUROD1,STMN1,TBR1,TUBB3</t>
+  </si>
+  <si>
+    <t>https://www.abcam.com/neuroscience/neural-markers-guide</t>
+  </si>
+  <si>
+    <t>DLG4,GAP43,INA,MAP2,MAPT,NEFH,NEFM,NRP1,RBFOX3,SYP,TUBB3,CALB2</t>
+  </si>
+  <si>
+    <t>PMID: 28817799</t>
+  </si>
+  <si>
+    <t>GLS,GRIN1,GRIN2B,SLC17A6,SLC17A7,GRIN2A,SATB2</t>
+  </si>
+  <si>
+    <t>PMID: 34616062;https://www.abcam.com/neuroscience/neural-markers-guide; scType</t>
+  </si>
+  <si>
+    <t>GABBR1,GABBR2,GAD1,GAD2,SLC6A1,SLC32A1</t>
+  </si>
+  <si>
+    <t>DBH,FOXA2,KCNJ6,LMX1B,NR4A2,PPP1R1B,SLC6A2,SLC6A3,TH</t>
+  </si>
+  <si>
+    <t>https://www.abcam.com/neuroscience/neural-markers-guide; scType</t>
+  </si>
+  <si>
+    <t>FEV,SLC6A4,TPH1</t>
+  </si>
+  <si>
+    <t>ACHE,CHAT,SLC18A3</t>
+  </si>
+  <si>
+    <t>Pyramidal neurons</t>
+  </si>
+  <si>
+    <t>EMX1,SATB2</t>
+  </si>
+  <si>
+    <t>Cortical glutamatergic neurons</t>
+  </si>
+  <si>
+    <t>TBR1,BCL11B,SATB2,SLC17A7</t>
+  </si>
+  <si>
+    <t>Subplate neurons</t>
+  </si>
+  <si>
+    <t>NR4A2,CRYM,ST18,CDH18</t>
+  </si>
+  <si>
+    <t>MGE interneurons</t>
+  </si>
+  <si>
+    <t>LHX6,SST,DLX5,GAD2</t>
+  </si>
+  <si>
+    <t>Neuron - Cortical interneurons</t>
+  </si>
+  <si>
+    <t>CGE interneurons</t>
+  </si>
+  <si>
+    <t>SP8,NR2F2,DLX5,GAD2</t>
+  </si>
+  <si>
+    <t>PSB interneurons</t>
+  </si>
+  <si>
+    <t>MEIS2,PAX6,ETV1</t>
+  </si>
+  <si>
+    <t>Neurons (mixed)</t>
+  </si>
+  <si>
+    <t>DYNC1I1,SATB2,HCN1,CNTN5,STMN2,NEUROD1</t>
+  </si>
+  <si>
+    <t>LIAS,DNAAF1,DNAH3,CFAP157,IL16,RSPH1,FOXJ1</t>
+  </si>
+  <si>
+    <t>Ependyma</t>
+  </si>
+  <si>
+    <t>https://www.proteinatlas.org/humanproteome/brain/cell+types; Aubin et al.,Nat Comm 2022</t>
+  </si>
+  <si>
+    <t>DCN</t>
+  </si>
+  <si>
+    <t>PMID: 34616062</t>
+  </si>
+  <si>
+    <t>AIF1,CCL3,CCL4,RGS10,TYROBP,CD83,GPR183,LAPTM5,ITGAM,P2RY12,APBB1IP,CD14,FCER1G,CSF1R,C1QC</t>
+  </si>
+  <si>
+    <t>PMID: 34390642;PMID: 26060301;PMID: 34616062; PMID: 32663469;</t>
+  </si>
+  <si>
+    <t>CLDN5,PECAM1</t>
+  </si>
+  <si>
+    <t>FOXC2,PDGFRB</t>
+  </si>
+  <si>
+    <t>Peric</t>
+  </si>
+  <si>
+    <t>Vascular-leptomeningeal cells</t>
+  </si>
+  <si>
+    <t>COL1A1,LUM</t>
+  </si>
+  <si>
+    <t>VLMC</t>
+  </si>
+  <si>
+    <t>Red blood cells</t>
+  </si>
+  <si>
+    <t>HEMGN</t>
+  </si>
+  <si>
+    <t>RBC</t>
+  </si>
+  <si>
+    <t>CD34,VWF,CLDN5,FLT1,LEF1,A2M,APOLD1,TM4SF1,CDH5,ENG,ETS1,FOXC1,GATA2,MCAM,PECAM1,VCAM1,XDH,IFITM1,CAV1</t>
+  </si>
+  <si>
+    <t>Vascular</t>
+  </si>
+  <si>
+    <t>PMID: 26060301;PMID: 29545511;www.proteinatlas.org/ENSG00000185736-ADARB2/single+cell+type/brain; PMID: 32663469</t>
+  </si>
+  <si>
+    <t>Cell cycle</t>
+  </si>
+  <si>
+    <t>CellCycling</t>
+  </si>
+  <si>
+    <t>Purkinje cells</t>
+  </si>
+  <si>
+    <t>CALB1,CA8,ITPR1,FOXP2,BCL11A,SKOR2</t>
+  </si>
+  <si>
+    <t>Purk</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Cerebellum</t>
+  </si>
+  <si>
+    <t>PMID: 15582153;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Rhombic lip</t>
+  </si>
+  <si>
+    <t>LMX1A,EOMES,PAX6,WLS,MKI67,OTX2</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>PMID: 31624095;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Granule cell progenitors</t>
+  </si>
+  <si>
+    <t>PAX6,MKI67,RBFOX3</t>
+  </si>
+  <si>
+    <t>GCP</t>
+  </si>
+  <si>
+    <t>PMID: 10409504;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Granule neurons</t>
+  </si>
+  <si>
+    <t>RBFOX3,RELN</t>
+  </si>
+  <si>
+    <t>MKI67</t>
+  </si>
+  <si>
+    <t>GN</t>
+  </si>
+  <si>
+    <t>PMID: 9348346;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Excitatory cerebellar nuclei neurons/Unipolar brush cells</t>
+  </si>
+  <si>
+    <t>LMX1A,EOMES,PAX6</t>
+  </si>
+  <si>
+    <t>eCN/UBC</t>
+  </si>
+  <si>
+    <t>PMID: 16957075;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Inhibitory cerebellar nuclei neurons</t>
+  </si>
+  <si>
+    <t>MEIS2</t>
+  </si>
+  <si>
+    <t>iCN</t>
+  </si>
+  <si>
+    <t>PMID: 17122047;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>PAX2+ interneuron progenitors</t>
+  </si>
+  <si>
+    <t>PAX2</t>
+  </si>
+  <si>
+    <t>PIP</t>
+  </si>
+  <si>
+    <t>PMID: 29545511;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Molecular layer interneurons</t>
+  </si>
+  <si>
+    <t>PTPRK,SORCS3</t>
+  </si>
+  <si>
+    <t>MLI</t>
+  </si>
+  <si>
+    <t>PMID: 24259518;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>Bergmann glia</t>
+  </si>
+  <si>
+    <t>GRIA1,SOX2,SLC1A3</t>
+  </si>
+  <si>
+    <t>PAX6</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>Astro</t>
+  </si>
+  <si>
+    <t>AQP4,SOX2,GFAP,SLC1A3</t>
+  </si>
+  <si>
+    <t>SOX2,SLC1A3</t>
+  </si>
+  <si>
+    <t>cOPC</t>
+  </si>
+  <si>
+    <t>BCAS1,GPR17,MOG</t>
+  </si>
+  <si>
+    <t>Committed oligodendrocyte precursor cells</t>
+  </si>
+  <si>
+    <t>FLT1,CLDN5,BSG,ITM2A,KDR</t>
+  </si>
+  <si>
+    <t>CSF1R,CX3CR1,CCL3,CD53</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>Meninges</t>
+  </si>
+  <si>
+    <t>COL3A1,FOXC1,CXCL12,DCN,IGF2,COL1A1</t>
+  </si>
+  <si>
+    <t>Menin</t>
+  </si>
+  <si>
+    <t>Brainstem</t>
+  </si>
+  <si>
+    <t>HOXB3</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>PMID: 11566863;PMID: 34140698;</t>
+  </si>
+  <si>
+    <t>TTR,FOLR1,PRLR</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>PMID: 25784853;PMID: 34140698;PMID: 34983929</t>
+  </si>
+  <si>
+    <t>HOXB3,TTR,DNAH5,DNAH9,DNAH11,FOXJ1</t>
+  </si>
+  <si>
+    <t>Choroid plexus/ependymal cells</t>
+  </si>
+  <si>
+    <t>Unipolar brush cells</t>
+  </si>
+  <si>
+    <t>LMX1A,EOMES</t>
+  </si>
+  <si>
+    <t>UBC</t>
+  </si>
+  <si>
+    <t>MBP,PLP1,OLIG2</t>
+  </si>
+  <si>
+    <t>PMID: 34616062;https://www.proteinatlas.org/humanproteome/brain/human+brain;PMID: 34390642 Table S1G;PMID: 26060302</t>
+  </si>
+  <si>
+    <t>Schwann</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -784,6 +1339,27 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -811,10 +1387,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -837,8 +1414,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1151,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K234"/>
+  <dimension ref="A1:K266"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1182,22 +1786,22 @@
         <v>123</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -1215,7 +1819,7 @@
         <v>124</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -1233,7 +1837,7 @@
         <v>125</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -1251,7 +1855,7 @@
         <v>126</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -1269,7 +1873,7 @@
         <v>127</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -1280,7 +1884,7 @@
         <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>71</v>
@@ -1289,7 +1893,7 @@
         <v>128</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -1306,10 +1910,10 @@
         <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -1326,10 +1930,10 @@
         <v>98</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -1344,10 +1948,10 @@
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -1362,10 +1966,10 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -1382,10 +1986,10 @@
         <v>122</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -1402,10 +2006,10 @@
         <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -1413,7 +2017,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>110</v>
@@ -1422,10 +2026,10 @@
         <v>122</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -1443,7 +2047,7 @@
         <v>58</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -1461,7 +2065,7 @@
         <v>129</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -1479,7 +2083,7 @@
         <v>130</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
@@ -1499,7 +2103,7 @@
         <v>131</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
@@ -1517,7 +2121,7 @@
         <v>52</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -1535,7 +2139,7 @@
         <v>56</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -1553,7 +2157,7 @@
         <v>51</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -1571,7 +2175,7 @@
         <v>132</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
@@ -1591,10 +2195,10 @@
         <v>49</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
@@ -1614,10 +2218,10 @@
         <v>49</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
@@ -1637,10 +2241,10 @@
         <v>49</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -1660,7 +2264,7 @@
         <v>55</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -1678,7 +2282,7 @@
         <v>133</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -1696,7 +2300,7 @@
         <v>134</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -1711,10 +2315,10 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -1734,7 +2338,7 @@
         <v>135</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -1752,7 +2356,7 @@
         <v>136</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -1770,7 +2374,7 @@
         <v>137</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -1788,7 +2392,7 @@
         <v>138</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -1806,7 +2410,7 @@
         <v>139</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -1824,7 +2428,7 @@
         <v>140</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -1839,10 +2443,10 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2" t="s">
-        <v>6</v>
+        <v>304</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -1860,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -1878,7 +2482,7 @@
         <v>10</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -1893,10 +2497,16 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2" t="s">
-        <v>67</v>
+        <v>266</v>
+      </c>
+      <c r="G38" t="s">
+        <v>354</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -1914,7 +2524,7 @@
         <v>13</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -1932,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -1950,7 +2560,7 @@
         <v>17</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -1968,7 +2578,7 @@
         <v>50</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -1986,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -2001,10 +2611,10 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -2019,10 +2629,16 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>142</v>
+        <v>423</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -2037,10 +2653,10 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -2055,10 +2671,10 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -2076,7 +2692,7 @@
         <v>30</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -2091,10 +2707,10 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -2109,10 +2725,16 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>146</v>
+        <v>423</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -2127,10 +2749,10 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -2144,11 +2766,11 @@
         <v>39</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="2" t="s">
-        <v>38</v>
+      <c r="E52" t="s">
+        <v>298</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -2163,10 +2785,13 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2" t="s">
-        <v>147</v>
+        <v>277</v>
+      </c>
+      <c r="G53" t="s">
+        <v>278</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -2181,10 +2806,10 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -2202,7 +2827,7 @@
         <v>44</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -2210,17 +2835,19 @@
         <v>5</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D56" s="2"/>
+        <v>184</v>
+      </c>
       <c r="E56" s="2" t="s">
-        <v>46</v>
+        <v>304</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -2228,19 +2855,19 @@
         <v>5</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -2248,19 +2875,19 @@
         <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -2268,19 +2895,25 @@
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>168</v>
+        <v>4</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>193</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>168</v>
+        <v>266</v>
+      </c>
+      <c r="G59" t="s">
+        <v>354</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -2288,19 +2921,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>67</v>
+        <v>229</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
@@ -2308,19 +2941,19 @@
         <v>5</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -2328,19 +2961,19 @@
         <v>5</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -2357,10 +2990,10 @@
         <v>174</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -2368,19 +3001,19 @@
         <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>176</v>
+        <v>201</v>
+      </c>
+      <c r="E64" t="s">
+        <v>298</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
@@ -2388,19 +3021,19 @@
         <v>5</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.2">
@@ -2408,19 +3041,19 @@
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.2">
@@ -2437,50 +3070,59 @@
         <v>177</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>228</v>
+      <c r="E68" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>234</v>
+      </c>
+      <c r="C69" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69" t="s">
+        <v>236</v>
+      </c>
+      <c r="F69" t="s">
+        <v>237</v>
+      </c>
+      <c r="G69" t="s">
+        <v>238</v>
+      </c>
+      <c r="H69" t="s">
+        <v>234</v>
+      </c>
+      <c r="I69" t="s">
+        <v>239</v>
+      </c>
+      <c r="K69" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="70" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -2488,22 +3130,28 @@
         <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C70" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E70" t="s">
-        <v>230</v>
+        <v>236</v>
+      </c>
+      <c r="F70" t="s">
+        <v>172</v>
       </c>
       <c r="G70" t="s">
-        <v>231</v>
+        <v>238</v>
+      </c>
+      <c r="H70" t="s">
+        <v>241</v>
       </c>
       <c r="I70" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="K70" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -2511,526 +3159,1699 @@
         <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C71" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" t="s">
+        <v>236</v>
+      </c>
+      <c r="F71" t="s">
+        <v>245</v>
+      </c>
+      <c r="G71" t="s">
         <v>238</v>
       </c>
-      <c r="E71" t="s">
-        <v>235</v>
+      <c r="H71" t="s">
+        <v>243</v>
       </c>
       <c r="I71" t="s">
+        <v>239</v>
+      </c>
+      <c r="K71" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>246</v>
+      </c>
+      <c r="C72" t="s">
+        <v>247</v>
+      </c>
+      <c r="E72" t="s">
+        <v>236</v>
+      </c>
+      <c r="F72" t="s">
+        <v>248</v>
+      </c>
+      <c r="G72" t="s">
+        <v>238</v>
+      </c>
+      <c r="H72" t="s">
+        <v>246</v>
+      </c>
+      <c r="I72" t="s">
+        <v>239</v>
+      </c>
+      <c r="K72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>249</v>
+      </c>
+      <c r="C73" t="s">
+        <v>250</v>
+      </c>
+      <c r="E73" t="s">
+        <v>236</v>
+      </c>
+      <c r="F73" t="s">
+        <v>251</v>
+      </c>
+      <c r="G73" t="s">
+        <v>238</v>
+      </c>
+      <c r="H73" t="s">
+        <v>249</v>
+      </c>
+      <c r="I73" t="s">
+        <v>239</v>
+      </c>
+      <c r="K73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>5</v>
+      </c>
+      <c r="B74" t="s">
+        <v>252</v>
+      </c>
+      <c r="C74" t="s">
+        <v>253</v>
+      </c>
+      <c r="E74" t="s">
+        <v>236</v>
+      </c>
+      <c r="F74" t="s">
+        <v>254</v>
+      </c>
+      <c r="G74" t="s">
+        <v>238</v>
+      </c>
+      <c r="H74" t="s">
+        <v>252</v>
+      </c>
+      <c r="I74" t="s">
+        <v>239</v>
+      </c>
+      <c r="K74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75" t="s">
+        <v>256</v>
+      </c>
+      <c r="E75" t="s">
+        <v>236</v>
+      </c>
+      <c r="F75" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" t="s">
+        <v>238</v>
+      </c>
+      <c r="H75" t="s">
+        <v>255</v>
+      </c>
+      <c r="I75" t="s">
+        <v>239</v>
+      </c>
+      <c r="K75" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="10"/>
+      <c r="E77" t="s">
+        <v>274</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>5</v>
+      </c>
+      <c r="B78" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" t="s">
+        <v>276</v>
+      </c>
+      <c r="E78" t="s">
+        <v>277</v>
+      </c>
+      <c r="G78" t="s">
+        <v>278</v>
+      </c>
+      <c r="H78" t="s">
+        <v>40</v>
+      </c>
+      <c r="I78" t="s">
+        <v>228</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" t="s">
+        <v>281</v>
+      </c>
+      <c r="E79" t="s">
+        <v>277</v>
+      </c>
+      <c r="G79" t="s">
+        <v>278</v>
+      </c>
+      <c r="H79" t="s">
+        <v>280</v>
+      </c>
+      <c r="I79" t="s">
+        <v>228</v>
+      </c>
+      <c r="K79" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>283</v>
+      </c>
+      <c r="C80" t="s">
+        <v>284</v>
+      </c>
+      <c r="E80" t="s">
+        <v>277</v>
+      </c>
+      <c r="G80" t="s">
+        <v>278</v>
+      </c>
+      <c r="H80" t="s">
+        <v>283</v>
+      </c>
+      <c r="I80" t="s">
+        <v>228</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>285</v>
+      </c>
+      <c r="C81" t="s">
+        <v>286</v>
+      </c>
+      <c r="E81" t="s">
+        <v>277</v>
+      </c>
+      <c r="G81" t="s">
+        <v>278</v>
+      </c>
+      <c r="H81" t="s">
+        <v>285</v>
+      </c>
+      <c r="I81" t="s">
+        <v>228</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>5</v>
+      </c>
+      <c r="B82" t="s">
+        <v>287</v>
+      </c>
+      <c r="C82" t="s">
+        <v>288</v>
+      </c>
+      <c r="E82" t="s">
+        <v>277</v>
+      </c>
+      <c r="G82" t="s">
+        <v>278</v>
+      </c>
+      <c r="H82" t="s">
+        <v>287</v>
+      </c>
+      <c r="I82" t="s">
+        <v>228</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>289</v>
+      </c>
+      <c r="C83" t="s">
+        <v>290</v>
+      </c>
+      <c r="E83" t="s">
+        <v>277</v>
+      </c>
+      <c r="G83" t="s">
+        <v>278</v>
+      </c>
+      <c r="H83" t="s">
+        <v>289</v>
+      </c>
+      <c r="I83" t="s">
+        <v>228</v>
+      </c>
+      <c r="K83" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="E84" t="s">
+        <v>293</v>
+      </c>
+      <c r="G84" t="s">
+        <v>293</v>
+      </c>
+      <c r="I84" t="s">
+        <v>228</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>294</v>
+      </c>
+      <c r="C85" t="s">
+        <v>295</v>
+      </c>
+      <c r="E85" t="s">
+        <v>296</v>
+      </c>
+      <c r="G85" t="s">
+        <v>296</v>
+      </c>
+      <c r="I85" t="s">
+        <v>228</v>
+      </c>
+      <c r="K85" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" t="s">
+        <v>297</v>
+      </c>
+      <c r="E86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G86" t="s">
+        <v>299</v>
+      </c>
+      <c r="I86" t="s">
+        <v>228</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>5</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+      <c r="C87" t="s">
+        <v>301</v>
+      </c>
+      <c r="E87" t="s">
+        <v>225</v>
+      </c>
+      <c r="G87" t="s">
+        <v>225</v>
+      </c>
+      <c r="I87" t="s">
+        <v>228</v>
+      </c>
+      <c r="K87" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" t="s">
+        <v>303</v>
+      </c>
+      <c r="E88" t="s">
+        <v>304</v>
+      </c>
+      <c r="G88" t="s">
+        <v>299</v>
+      </c>
+      <c r="I88" t="s">
+        <v>228</v>
+      </c>
+      <c r="K88" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" t="s">
+        <v>308</v>
+      </c>
+      <c r="E89" t="s">
+        <v>309</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="H89" s="15"/>
+      <c r="I89" t="s">
+        <v>228</v>
+      </c>
+      <c r="J89" s="15"/>
+      <c r="K89" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>311</v>
+      </c>
+      <c r="E90" t="s">
+        <v>236</v>
+      </c>
+      <c r="G90" t="s">
+        <v>236</v>
+      </c>
+      <c r="I90" t="s">
+        <v>228</v>
+      </c>
+      <c r="K90" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" t="s">
+        <v>313</v>
+      </c>
+      <c r="E91" t="s">
+        <v>236</v>
+      </c>
+      <c r="G91" t="s">
+        <v>236</v>
+      </c>
+      <c r="I91" t="s">
+        <v>228</v>
+      </c>
+      <c r="K91" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>315</v>
+      </c>
+      <c r="E92" t="s">
+        <v>236</v>
+      </c>
+      <c r="G92" t="s">
+        <v>236</v>
+      </c>
+      <c r="I92" t="s">
+        <v>228</v>
+      </c>
+      <c r="K92" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
+        <v>317</v>
+      </c>
+      <c r="E93" t="s">
+        <v>236</v>
+      </c>
+      <c r="G93" t="s">
+        <v>236</v>
+      </c>
+      <c r="I93" t="s">
+        <v>228</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" t="s">
+        <v>318</v>
+      </c>
+      <c r="E94" t="s">
+        <v>236</v>
+      </c>
+      <c r="G94" t="s">
+        <v>236</v>
+      </c>
+      <c r="I94" t="s">
+        <v>228</v>
+      </c>
+      <c r="K94" s="16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" t="s">
+        <v>320</v>
+      </c>
+      <c r="E95" t="s">
+        <v>236</v>
+      </c>
+      <c r="G95" t="s">
+        <v>236</v>
+      </c>
+      <c r="I95" t="s">
+        <v>228</v>
+      </c>
+      <c r="K95" s="16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" t="s">
+        <v>321</v>
+      </c>
+      <c r="E96" t="s">
+        <v>236</v>
+      </c>
+      <c r="G96" t="s">
+        <v>236</v>
+      </c>
+      <c r="I96" t="s">
+        <v>228</v>
+      </c>
+      <c r="K96" s="16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>322</v>
+      </c>
+      <c r="C97" t="s">
+        <v>323</v>
+      </c>
+      <c r="E97" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97" t="s">
+        <v>236</v>
+      </c>
+      <c r="I97" t="s">
+        <v>228</v>
+      </c>
+      <c r="K97" s="16" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>324</v>
+      </c>
+      <c r="C98" t="s">
+        <v>325</v>
+      </c>
+      <c r="E98" t="s">
+        <v>236</v>
+      </c>
+      <c r="G98" t="s">
+        <v>236</v>
+      </c>
+      <c r="I98" t="s">
+        <v>228</v>
+      </c>
+      <c r="K98" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>326</v>
+      </c>
+      <c r="C99" t="s">
+        <v>327</v>
+      </c>
+      <c r="E99" t="s">
+        <v>236</v>
+      </c>
+      <c r="G99" t="s">
+        <v>236</v>
+      </c>
+      <c r="I99" t="s">
+        <v>228</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>328</v>
+      </c>
+      <c r="C100" t="s">
+        <v>329</v>
+      </c>
+      <c r="E100" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" t="s">
+        <v>330</v>
+      </c>
+      <c r="I100" t="s">
+        <v>228</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>331</v>
+      </c>
+      <c r="C101" t="s">
+        <v>332</v>
+      </c>
+      <c r="E101" t="s">
+        <v>236</v>
+      </c>
+      <c r="G101" t="s">
+        <v>330</v>
+      </c>
+      <c r="I101" t="s">
+        <v>228</v>
+      </c>
+      <c r="K101" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>333</v>
+      </c>
+      <c r="C102" t="s">
+        <v>334</v>
+      </c>
+      <c r="E102" t="s">
+        <v>236</v>
+      </c>
+      <c r="G102" t="s">
+        <v>236</v>
+      </c>
+      <c r="I102" t="s">
+        <v>228</v>
+      </c>
+      <c r="K102" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>335</v>
+      </c>
+      <c r="C103" t="s">
+        <v>336</v>
+      </c>
+      <c r="E103" t="s">
+        <v>236</v>
+      </c>
+      <c r="G103" t="s">
+        <v>236</v>
+      </c>
+      <c r="I103" t="s">
+        <v>228</v>
+      </c>
+      <c r="K103" s="9" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>229</v>
+      </c>
+      <c r="C104" t="s">
+        <v>337</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="I104" t="s">
+        <v>228</v>
+      </c>
+      <c r="K104" s="17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>261</v>
+      </c>
+      <c r="C105" t="s">
+        <v>340</v>
+      </c>
+      <c r="E105" t="s">
+        <v>263</v>
+      </c>
+      <c r="G105" t="s">
+        <v>261</v>
+      </c>
+      <c r="I105" t="s">
+        <v>228</v>
+      </c>
+      <c r="K105" s="9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>5</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" t="s">
+        <v>342</v>
+      </c>
+      <c r="E106" t="s">
+        <v>212</v>
+      </c>
+      <c r="G106" t="s">
+        <v>299</v>
+      </c>
+      <c r="I106" t="s">
+        <v>228</v>
+      </c>
+      <c r="K106" s="12" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A107" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="F107" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="G107" t="s">
+        <v>354</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I107" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="K107" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A108" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="F108" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="I108" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="K108" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A109" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D109" s="13"/>
+      <c r="E109" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="F109" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="I109" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="K109" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A110" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="D110" s="13"/>
+      <c r="E110" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="I110" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="K110" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>353</v>
+      </c>
+      <c r="E111" t="s">
+        <v>266</v>
+      </c>
+      <c r="G111" t="s">
+        <v>354</v>
+      </c>
+      <c r="H111" t="s">
+        <v>67</v>
+      </c>
+      <c r="K111" s="9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>356</v>
+      </c>
+      <c r="C112" t="s">
+        <v>272</v>
+      </c>
+      <c r="D112" t="s">
+        <v>77</v>
+      </c>
+      <c r="E112" t="s">
+        <v>357</v>
+      </c>
+      <c r="G112" t="s">
+        <v>227</v>
+      </c>
+      <c r="I112" t="s">
+        <v>228</v>
+      </c>
+      <c r="K112" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>229</v>
+      </c>
+      <c r="C113" t="s">
         <v>232</v>
       </c>
-      <c r="K71" t="s">
+      <c r="E113" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="I113" t="s">
+        <v>228</v>
+      </c>
+      <c r="K113" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>261</v>
+      </c>
+      <c r="C114" t="s">
+        <v>262</v>
+      </c>
+      <c r="E114" t="s">
+        <v>263</v>
+      </c>
+      <c r="I114" t="s">
+        <v>228</v>
+      </c>
+      <c r="K114" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>5</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" t="s">
+        <v>265</v>
+      </c>
+      <c r="E115" t="s">
+        <v>266</v>
+      </c>
+      <c r="G115" t="s">
+        <v>354</v>
+      </c>
+      <c r="H115" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K115" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A116" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E116" s="8" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="4"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" s="2"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G116" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="K116" s="19" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>358</v>
+      </c>
+      <c r="C117" t="s">
+        <v>359</v>
+      </c>
+      <c r="E117" t="s">
+        <v>360</v>
+      </c>
+      <c r="F117" t="s">
+        <v>361</v>
+      </c>
+      <c r="G117" t="s">
+        <v>358</v>
+      </c>
+      <c r="I117" t="s">
+        <v>362</v>
+      </c>
+      <c r="K117" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s">
+        <v>364</v>
+      </c>
+      <c r="C118" t="s">
+        <v>365</v>
+      </c>
+      <c r="E118" t="s">
+        <v>366</v>
+      </c>
+      <c r="F118" t="s">
+        <v>366</v>
+      </c>
+      <c r="G118" t="s">
+        <v>364</v>
+      </c>
+      <c r="I118" t="s">
+        <v>362</v>
+      </c>
+      <c r="K118" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>5</v>
+      </c>
+      <c r="B119" t="s">
+        <v>368</v>
+      </c>
+      <c r="C119" t="s">
+        <v>369</v>
+      </c>
+      <c r="E119" t="s">
+        <v>370</v>
+      </c>
+      <c r="F119" t="s">
+        <v>370</v>
+      </c>
+      <c r="G119" t="s">
+        <v>368</v>
+      </c>
+      <c r="I119" t="s">
+        <v>362</v>
+      </c>
+      <c r="K119" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>372</v>
+      </c>
+      <c r="C120" t="s">
+        <v>373</v>
+      </c>
+      <c r="D120" t="s">
+        <v>374</v>
+      </c>
+      <c r="E120" t="s">
+        <v>236</v>
+      </c>
+      <c r="F120" t="s">
+        <v>375</v>
+      </c>
+      <c r="G120" t="s">
+        <v>372</v>
+      </c>
+      <c r="I120" t="s">
+        <v>362</v>
+      </c>
+      <c r="K120" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>5</v>
+      </c>
+      <c r="B121" t="s">
+        <v>377</v>
+      </c>
+      <c r="C121" t="s">
+        <v>378</v>
+      </c>
+      <c r="D121" t="s">
+        <v>374</v>
+      </c>
+      <c r="E121" t="s">
+        <v>236</v>
+      </c>
+      <c r="F121" t="s">
+        <v>379</v>
+      </c>
+      <c r="G121" t="s">
+        <v>377</v>
+      </c>
+      <c r="I121" t="s">
+        <v>362</v>
+      </c>
+      <c r="K121" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>5</v>
+      </c>
+      <c r="B122" t="s">
+        <v>381</v>
+      </c>
+      <c r="C122" t="s">
+        <v>382</v>
+      </c>
+      <c r="E122" t="s">
+        <v>236</v>
+      </c>
+      <c r="F122" t="s">
+        <v>383</v>
+      </c>
+      <c r="G122" t="s">
+        <v>381</v>
+      </c>
+      <c r="I122" t="s">
+        <v>362</v>
+      </c>
+      <c r="K122" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
+        <v>385</v>
+      </c>
+      <c r="C123" t="s">
+        <v>386</v>
+      </c>
+      <c r="E123" t="s">
+        <v>236</v>
+      </c>
+      <c r="F123" t="s">
+        <v>387</v>
+      </c>
+      <c r="G123" t="s">
+        <v>385</v>
+      </c>
+      <c r="I123" t="s">
+        <v>362</v>
+      </c>
+      <c r="K123" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>389</v>
+      </c>
+      <c r="C124" t="s">
+        <v>390</v>
+      </c>
+      <c r="E124" t="s">
+        <v>236</v>
+      </c>
+      <c r="F124" t="s">
+        <v>391</v>
+      </c>
+      <c r="G124" t="s">
+        <v>389</v>
+      </c>
+      <c r="I124" t="s">
+        <v>362</v>
+      </c>
+      <c r="K124" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>5</v>
+      </c>
+      <c r="B125" t="s">
+        <v>393</v>
+      </c>
+      <c r="C125" t="s">
+        <v>394</v>
+      </c>
+      <c r="D125" t="s">
+        <v>395</v>
+      </c>
+      <c r="E125" t="s">
+        <v>396</v>
+      </c>
+      <c r="F125" t="s">
+        <v>396</v>
+      </c>
+      <c r="G125" t="s">
+        <v>393</v>
+      </c>
+      <c r="I125" t="s">
+        <v>362</v>
+      </c>
+      <c r="K125" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>397</v>
+      </c>
+      <c r="C126" t="s">
+        <v>398</v>
+      </c>
+      <c r="E126" t="s">
+        <v>304</v>
+      </c>
+      <c r="F126" t="s">
+        <v>397</v>
+      </c>
+      <c r="G126" t="s">
+        <v>6</v>
+      </c>
+      <c r="I126" t="s">
+        <v>362</v>
+      </c>
+      <c r="K126" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>299</v>
+      </c>
+      <c r="C127" t="s">
+        <v>399</v>
+      </c>
+      <c r="E127" t="s">
+        <v>299</v>
+      </c>
+      <c r="F127" t="s">
+        <v>299</v>
+      </c>
+      <c r="G127" t="s">
+        <v>299</v>
+      </c>
+      <c r="I127" t="s">
+        <v>362</v>
+      </c>
+      <c r="K127" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>5</v>
+      </c>
+      <c r="B128" t="s">
+        <v>400</v>
+      </c>
+      <c r="C128" t="s">
+        <v>401</v>
+      </c>
+      <c r="E128" t="s">
+        <v>225</v>
+      </c>
+      <c r="F128" t="s">
+        <v>400</v>
+      </c>
+      <c r="G128" t="s">
+        <v>402</v>
+      </c>
+      <c r="I128" t="s">
+        <v>362</v>
+      </c>
+      <c r="K128" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>354</v>
+      </c>
+      <c r="C129" t="s">
+        <v>403</v>
+      </c>
+      <c r="E129" t="s">
+        <v>354</v>
+      </c>
+      <c r="F129" t="s">
+        <v>266</v>
+      </c>
+      <c r="G129" t="s">
+        <v>354</v>
+      </c>
+      <c r="H129" t="s">
+        <v>4</v>
+      </c>
+      <c r="I129" t="s">
+        <v>362</v>
+      </c>
+      <c r="K129" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>212</v>
+      </c>
+      <c r="C130" t="s">
+        <v>404</v>
+      </c>
+      <c r="E130" t="s">
+        <v>212</v>
+      </c>
+      <c r="F130" t="s">
+        <v>405</v>
+      </c>
+      <c r="G130" t="s">
+        <v>212</v>
+      </c>
+      <c r="I130" t="s">
+        <v>362</v>
+      </c>
+      <c r="K130" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>406</v>
+      </c>
+      <c r="C131" t="s">
+        <v>407</v>
+      </c>
+      <c r="E131" t="s">
+        <v>408</v>
+      </c>
+      <c r="F131" t="s">
+        <v>408</v>
+      </c>
+      <c r="G131" t="s">
+        <v>406</v>
+      </c>
+      <c r="I131" t="s">
+        <v>362</v>
+      </c>
+      <c r="K131" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>409</v>
+      </c>
+      <c r="C132" t="s">
+        <v>410</v>
+      </c>
+      <c r="E132" t="s">
+        <v>411</v>
+      </c>
+      <c r="F132" t="s">
+        <v>411</v>
+      </c>
+      <c r="G132" t="s">
+        <v>409</v>
+      </c>
+      <c r="I132" t="s">
+        <v>362</v>
+      </c>
+      <c r="K132" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>5</v>
+      </c>
+      <c r="B133" t="s">
+        <v>166</v>
+      </c>
+      <c r="C133" t="s">
+        <v>413</v>
+      </c>
+      <c r="E133" t="s">
+        <v>414</v>
+      </c>
+      <c r="F133" t="s">
+        <v>414</v>
+      </c>
+      <c r="G133" t="s">
+        <v>166</v>
+      </c>
+      <c r="I133" t="s">
+        <v>362</v>
+      </c>
+      <c r="K133" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>5</v>
+      </c>
+      <c r="B134" t="s">
+        <v>229</v>
+      </c>
+      <c r="C134" t="s">
+        <v>416</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F134" t="s">
+        <v>230</v>
+      </c>
+      <c r="G134" t="s">
+        <v>417</v>
+      </c>
+      <c r="I134" t="s">
+        <v>362</v>
+      </c>
+      <c r="K134" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" t="s">
+        <v>419</v>
+      </c>
+      <c r="E135" t="s">
+        <v>420</v>
+      </c>
+      <c r="F135" t="s">
+        <v>420</v>
+      </c>
+      <c r="G135" t="s">
+        <v>418</v>
+      </c>
+      <c r="I135" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>5</v>
+      </c>
+      <c r="B136" t="s">
+        <v>298</v>
+      </c>
+      <c r="C136" t="s">
+        <v>421</v>
+      </c>
+      <c r="E136" t="s">
+        <v>298</v>
+      </c>
+      <c r="F136" t="s">
+        <v>298</v>
+      </c>
+      <c r="G136" t="s">
+        <v>38</v>
+      </c>
+      <c r="I136" t="s">
+        <v>362</v>
+      </c>
+      <c r="K136" s="14" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -3667,19 +5488,252 @@
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
     </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A257" s="2"/>
+      <c r="B257" s="2"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A259" s="2"/>
+      <c r="B259" s="2"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A260" s="2"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A261" s="2"/>
+      <c r="B261" s="2"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="2"/>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A266" s="2"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E234">
-    <sortCondition ref="A35:A234"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E266">
+    <sortCondition ref="A35:A266"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="K104" r:id="rId1" xr:uid="{42A7C063-CDCE-7D47-8E33-A9891622F7A0}"/>
+    <hyperlink ref="K86" r:id="rId2" display="https://www.proteinatlas.org/humanproteome/brain/human+brain;PMID: 34390642 Table S1G;PMID: 26060302" xr:uid="{EBB5D4A4-490E-8544-98BB-D0F15A692487}"/>
+    <hyperlink ref="K94" r:id="rId3" xr:uid="{BC1345FB-EF91-AC43-A4C6-BDD87F544BE3}"/>
+    <hyperlink ref="K95" r:id="rId4" xr:uid="{EBACCA4B-83F2-3A4D-9D57-4D3613887CC9}"/>
+    <hyperlink ref="K96" r:id="rId5" xr:uid="{C980C444-B4D4-224A-AA00-05E9699B63FC}"/>
+    <hyperlink ref="K97" r:id="rId6" xr:uid="{EE8BFE7F-5919-534C-AFA5-73E58B26CEC4}"/>
+    <hyperlink ref="K136" r:id="rId7" display="https://www.proteinatlas.org/humanproteome/brain/human+brain;PMID: 34390642 Table S1G;PMID: 26060302" xr:uid="{E402F09B-F488-2149-8101-47F30446B87A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D0E990-649A-C44A-8355-B01009430605}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
@@ -3691,19 +5745,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3711,19 +5765,19 @@
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3731,19 +5785,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3751,19 +5805,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3771,19 +5825,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3791,19 +5845,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3811,19 +5865,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3831,19 +5885,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3851,19 +5905,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3871,19 +5925,19 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3891,19 +5945,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3911,19 +5965,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3931,19 +5985,19 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -3951,19 +6005,40 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
